--- a/Thread_3/Combined_Features_Scaled.xlsx
+++ b/Thread_3/Combined_Features_Scaled.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,25 +485,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9587913500123313</v>
+        <v>1.016969113922396</v>
       </c>
       <c r="D2" t="n">
-        <v>1.809062240573392</v>
+        <v>1.820632470927325</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1352503284696005</v>
+        <v>0.1071501770574141</v>
       </c>
       <c r="F2" t="n">
-        <v>1.317843833656484</v>
+        <v>1.473942667532741</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9369204359084604</v>
+        <v>1.076807137220409</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9708980278117203</v>
+        <v>0.8895508163184108</v>
       </c>
       <c r="I2" t="n">
-        <v>1.277876307262351</v>
+        <v>1.408119495376224</v>
       </c>
     </row>
     <row r="3">
@@ -516,25 +516,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-1.045932813537918</v>
+        <v>-1.061962702401142</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4024169660321613</v>
+        <v>0.4937907910792503</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.193371540319902</v>
+        <v>-1.272168623413758</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4655406241087562</v>
+        <v>0.5795896294977383</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3121090224045293</v>
+        <v>0.4065868227141025</v>
       </c>
       <c r="H3" t="n">
-        <v>1.099992092466443</v>
+        <v>1.019462627223163</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7560191071503348</v>
+        <v>0.8435575620838569</v>
       </c>
     </row>
     <row r="4">
@@ -547,25 +547,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0901707758957026</v>
+        <v>0.1161953413120505</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5703927047668643</v>
+        <v>-0.4238282001027355</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3386872569985249</v>
+        <v>0.3183497567284246</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09812398332382861</v>
+        <v>0.1940458638172289</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1838142849583718</v>
+        <v>0.2689681150172293</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1753882153600049</v>
+        <v>0.08900184759151011</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1588742890743918</v>
+        <v>0.1975470579150732</v>
       </c>
     </row>
     <row r="5">
@@ -578,25 +578,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.4394521911868811</v>
+        <v>-0.4330323564145842</v>
       </c>
       <c r="D5" t="n">
-        <v>1.003403377348878</v>
+        <v>1.060681274408396</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8686548528490617</v>
+        <v>-0.9350615484991178</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7469056089557715</v>
+        <v>-0.6926747006703541</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4610547201560291</v>
+        <v>-0.4227675000531627</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3800646163427593</v>
+        <v>-0.4699694996325372</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6416166458969499</v>
+        <v>-0.6684498273122069</v>
       </c>
     </row>
     <row r="6">
@@ -605,29 +605,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NamABank</t>
+          <t>LP Bank</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.1792918995680832</v>
+        <v>-0.404048195676216</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7113378571983968</v>
+        <v>-1.13641479841573</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4873194483157784</v>
+        <v>0.1575441471199499</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2302757246067631</v>
+        <v>-0.07490644705701682</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.004211713637289055</v>
+        <v>-0.05778730081587168</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9852601326081218</v>
+        <v>-0.5584346202364716</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5233147430022774</v>
+        <v>-0.2967716392213052</v>
       </c>
     </row>
     <row r="7">
@@ -636,29 +636,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OCB</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.7517095198993609</v>
+        <v>0.2873843966682268</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5468489044398881</v>
+        <v>-2.169168442155544</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9710787762036814</v>
+        <v>1.330415288836173</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.324428054851262</v>
+        <v>-0.1317954067988771</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3597512284606677</v>
+        <v>-0.1878853831717743</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1374600537427007</v>
+        <v>0.7121814787768813</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2978660016075538</v>
+        <v>0.2029786458752511</v>
       </c>
     </row>
     <row r="8">
@@ -667,29 +667,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PVcomBank</t>
+          <t>NamABank</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-1.372572091102115</v>
+        <v>0.2086154073130022</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.145742833657919</v>
+        <v>-0.5567770722906368</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3890813810608469</v>
+        <v>0.472653385665302</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.179874645953729</v>
+        <v>0.3327175360273166</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.823736100734036</v>
+        <v>0.0672771068337603</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9991402998262452</v>
+        <v>0.9040038978562389</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.918956051692365</v>
+        <v>0.5918104832262716</v>
       </c>
     </row>
     <row r="9">
@@ -698,29 +698,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SHB</t>
+          <t>OCB</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-1.274719585335898</v>
+        <v>0.8022218618904985</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.08283412669629053</v>
+        <v>-0.4016201166994473</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.202063216314403</v>
+        <v>0.9748717756629142</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.09963021211462825</v>
+        <v>-0.2493534978610074</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.071204358240841</v>
+        <v>-0.3141016584932358</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.593093110759515</v>
+        <v>-0.2258281586233639</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9061069411197565</v>
+        <v>-0.2965693046924908</v>
       </c>
     </row>
     <row r="10">
@@ -729,29 +729,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Techcombank</t>
+          <t>PVcomBank</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-1.10403095527955</v>
+        <v>-1.40069298706363</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.898110065110688</v>
+        <v>-1.909803555224451</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6773510521323751</v>
+        <v>-0.4371887365399186</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9429244041406318</v>
+        <v>-2.196341702381261</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.733541834856697</v>
+        <v>-1.884483345385002</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9855765222224481</v>
+        <v>-1.092966717541382</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2423073395103737</v>
+        <v>-2.050316752309298</v>
       </c>
     </row>
     <row r="11">
@@ -760,29 +760,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TPBank</t>
+          <t>SeABank</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.004762434760944</v>
+        <v>-1.168058314275549</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7017003312987087</v>
+        <v>-0.6983513259018586</v>
       </c>
       <c r="E11" t="n">
-        <v>1.285109393026629</v>
+        <v>-0.7978154975564684</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5941867453942128</v>
+        <v>-1.033591306369262</v>
       </c>
       <c r="G11" t="n">
-        <v>1.912446739459837</v>
+        <v>-0.5282075763127916</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4803230481110013</v>
+        <v>0.154724083440586</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2429329769816294</v>
+        <v>-0.6030604196024254</v>
       </c>
     </row>
     <row r="12">
@@ -791,29 +791,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vietcombank</t>
+          <t>SHB</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.1743340559148049</v>
+        <v>-1.299218334718386</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3407958546364102</v>
+        <v>0.03606958255784731</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3193963411587905</v>
+        <v>-1.28119195231451</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.06711243128973263</v>
+        <v>-0.01346487120441069</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4950224499110576</v>
+        <v>-1.077260477445834</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.038046824606618</v>
+        <v>-1.690681922083795</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5528726108300637</v>
+        <v>-0.9545839505474619</v>
       </c>
     </row>
     <row r="13">
@@ -822,29 +822,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VietinBank</t>
+          <t>Techcombank</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.1835253811789145</v>
+        <v>-1.122211427653226</v>
       </c>
       <c r="D13" t="n">
-        <v>1.594387433174301</v>
+        <v>-0.7329530809692303</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5235067680147308</v>
+        <v>-0.7364580668549949</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.970333726552983</v>
+        <v>-0.8983644165152216</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2942427407815171</v>
+        <v>-0.7150579348412088</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.272856078982079</v>
+        <v>0.9043222916403257</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.092615345715195</v>
+        <v>-0.2364641539386282</v>
       </c>
     </row>
     <row r="14">
@@ -853,122 +853,122 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VPBank</t>
+          <t>TPBank</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.7817891982125449</v>
+        <v>1.064641882302434</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.6894692563855598</v>
+        <v>-0.5476863148084478</v>
       </c>
       <c r="E14" t="n">
-        <v>1.063083331840539</v>
+        <v>1.300885025845292</v>
       </c>
       <c r="F14" t="n">
-        <v>2.206726328553413</v>
+        <v>-0.5324211922223321</v>
       </c>
       <c r="G14" t="n">
-        <v>0.639578166660796</v>
+        <v>2.123230957023542</v>
       </c>
       <c r="H14" t="n">
-        <v>1.963432292753269</v>
+        <v>0.3958682897983899</v>
       </c>
       <c r="I14" t="n">
-        <v>2.100028506102306</v>
+        <v>0.2884844548595694</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ACB</t>
+          <t>Vietcombank</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.472959034597172</v>
+        <v>-0.158100504680224</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4350343810805004</v>
+        <v>0.4356656472080567</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.6510243267590093</v>
+        <v>-0.3648446874869984</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2839284649015226</v>
+        <v>0.02065722964551362</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.9496802731605655</v>
+        <v>-0.4592038743373806</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3840053396756662</v>
+        <v>-1.132119695672077</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4891240585553941</v>
+        <v>-0.572443670848767</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Agribank</t>
+          <t>VietinBank</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-1.175727559180468</v>
+        <v>0.2130055971329282</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.079651614522524</v>
+        <v>1.618136868641687</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6671005310945981</v>
+        <v>-0.5767434645190952</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5427242880990574</v>
+        <v>-0.9271260244680712</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1825127658857056</v>
+        <v>-0.2438322647750038</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6373365435198803</v>
+        <v>-1.368416349082895</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5145501547351048</v>
+        <v>-1.156354751929668</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BIDV</t>
+          <t>VPBank</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.8786814895770552</v>
+        <v>0.833414981326597</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.232199316335585</v>
+        <v>-0.5361491488449798</v>
       </c>
       <c r="E17" t="n">
-        <v>1.396124647320316</v>
+        <v>1.070386998089995</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3185475565371121</v>
+        <v>2.40667969217571</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4844158882941251</v>
+        <v>0.7578551704283769</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4032494824665413</v>
+        <v>1.888372288772966</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4267105873189576</v>
+        <v>2.297550233781338</v>
       </c>
     </row>
     <row r="18">
@@ -977,29 +977,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HDBank</t>
+          <t>ACB</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.5386080799114806</v>
+        <v>-0.4677795022298287</v>
       </c>
       <c r="D18" t="n">
-        <v>2.363479835895042</v>
+        <v>0.524557713314961</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5170471226556661</v>
+        <v>-0.7091267786116294</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5686824590880387</v>
+        <v>-0.2068557917571647</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2684975559501101</v>
+        <v>-0.9469044872025787</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3744553443651514</v>
+        <v>-0.4739351854742668</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5074116539068211</v>
+        <v>-0.5034784330230712</v>
       </c>
     </row>
     <row r="19">
@@ -1008,29 +1008,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NCB</t>
+          <t>Agribank</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-1.506934384425244</v>
+        <v>-1.196561981052054</v>
       </c>
       <c r="D19" t="n">
-        <v>1.29218651895421</v>
+        <v>-0.9041951835401028</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.032944302345297</v>
+        <v>-0.7258164112311019</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2763034821209525</v>
+        <v>0.6605812808292274</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.823736100734036</v>
+        <v>-0.1239821831407614</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.473181902890161</v>
+        <v>0.5538763870692371</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.095185482033189</v>
+        <v>0.5823286692442772</v>
       </c>
     </row>
     <row r="20">
@@ -1039,29 +1039,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OCB</t>
+          <t>BIDV</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.08326353351251772</v>
+        <v>0.9338938755987374</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4169623426924173</v>
+        <v>-1.048088354472354</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2644388063569241</v>
+        <v>1.416136348274511</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9275027461783072</v>
+        <v>0.4253444089235424</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2938797691374341</v>
+        <v>0.5914162918182138</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3277847512171556</v>
+        <v>0.3183065017135666</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5728076671262479</v>
+        <v>0.4873009950273062</v>
       </c>
     </row>
     <row r="21">
@@ -1070,29 +1070,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SHB</t>
+          <t>HDBank</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.5868151006048229</v>
+        <v>0.5812321757530317</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2732980826722733</v>
+        <v>2.343596139755507</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4498521530975941</v>
+        <v>-0.5700373350345248</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4394005204112181</v>
+        <v>-0.5056586085721482</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1347499559555228</v>
+        <v>-0.2162160184936448</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.256885786595636</v>
+        <v>-0.4643246957260421</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2513046729978103</v>
+        <v>-0.5232625428995927</v>
       </c>
     </row>
     <row r="22">
@@ -1101,29 +1101,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Techcombank</t>
+          <t>LP Bank</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.032871823829432</v>
+        <v>-0.4188944747011181</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.04444184324281189</v>
+        <v>0.01348210651803219</v>
       </c>
       <c r="E22" t="n">
-        <v>1.023107085183057</v>
+        <v>-0.4139798890921251</v>
       </c>
       <c r="F22" t="n">
-        <v>1.493874949676698</v>
+        <v>-1.026639965065306</v>
       </c>
       <c r="G22" t="n">
-        <v>2.099515273273481</v>
+        <v>-0.414563009657279</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7394770178847291</v>
+        <v>1.903566488083595</v>
       </c>
       <c r="I22" t="n">
-        <v>1.499424816337672</v>
+        <v>0.1880331742891031</v>
       </c>
     </row>
     <row r="23">
@@ -1132,29 +1132,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TPBank</t>
+          <t>NCB</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.9116670461421217</v>
+        <v>-1.540028887524356</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4185218451807305</v>
+        <v>1.333080802316662</v>
       </c>
       <c r="E23" t="n">
-        <v>1.07000718371871</v>
+        <v>-2.143777410103545</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.09474058309336841</v>
+        <v>-0.1988546174821245</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8279653283059911</v>
+        <v>-1.884483345385002</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1159087039605733</v>
+        <v>-1.570011136763425</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1545016339963419</v>
+        <v>-1.159135208208129</v>
       </c>
     </row>
     <row r="24">
@@ -1163,29 +1163,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>VietAbank</t>
+          <t>OCB</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.294734831222923</v>
+        <v>-0.06365888024445664</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6963005785038334</v>
+        <v>0.5075109608698974</v>
       </c>
       <c r="E24" t="n">
-        <v>1.923079176379858</v>
+        <v>-0.3077901087837084</v>
       </c>
       <c r="F24" t="n">
-        <v>2.154201679186925</v>
+        <v>-0.8821819048273205</v>
       </c>
       <c r="G24" t="n">
-        <v>1.560634889518114</v>
+        <v>0.3870327371231056</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8993738330150931</v>
+        <v>-0.4173584677428158</v>
       </c>
       <c r="I24" t="n">
-        <v>1.81444520836366</v>
+        <v>-0.594010057056431</v>
       </c>
     </row>
     <row r="25">
@@ -1194,29 +1194,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vietcombank</t>
+          <t>SeABank</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.6593060304377072</v>
+        <v>1.113760600457718</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4225657087490579</v>
+        <v>1.021141755172412</v>
       </c>
       <c r="E25" t="n">
-        <v>0.826591716907863</v>
+        <v>0.5886211751096686</v>
       </c>
       <c r="F25" t="n">
-        <v>0.04214252906834338</v>
+        <v>-0.1011668136270811</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.4405338249148825</v>
+        <v>-0.6782244340002673</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3852197719907481</v>
+        <v>0.06289404119981711</v>
       </c>
       <c r="I25" t="n">
-        <v>0.09531816986116819</v>
+        <v>-0.1586448212455258</v>
       </c>
     </row>
     <row r="26">
@@ -1225,29 +1225,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>VietinBank</t>
+          <t>SHB</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-1.810217102085366</v>
+        <v>-0.5858501088541127</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3740092431830396</v>
+        <v>-0.1435887292223592</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.594185737435241</v>
+        <v>-0.5002783712648107</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.598380016888877</v>
+        <v>0.5521598593237541</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.40732081245176</v>
+        <v>0.2163379784598352</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.879775221652049</v>
+        <v>-1.352344892892014</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.887462092978673</v>
+        <v>-0.2461977591989429</v>
       </c>
     </row>
     <row r="27">
@@ -1256,29 +1256,184 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>Techcombank</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1.093791779497471</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.07228374599520077</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.028885356515199</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.658658578065229</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.323894915550966</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.6566638701878306</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.647797810775067</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TPBank</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.9681004384112566</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.2805734719204951</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.077575047068852</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.008334004018836692</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.9599335896088529</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.02914556327435722</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.1928165787649251</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>VietAbank</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2.402364400913014</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.7710014234321082</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.963198161721459</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.35156364989591</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.745850768987807</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.8175735515666486</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.98859702080903</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Vietcombank</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7063979287659784</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-0.284387913860611</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8248714467558713</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.1353024692997089</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-0.4007552247246076</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.3001625820510836</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.1287900003754324</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>VietinBank</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>-1.854538036737238</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-0.2385862156605347</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-1.688276901144157</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-1.586158046753406</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-1.437804588489942</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-1.979180020580096</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-2.016245573039154</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>VPBank</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>0.7810485461141455</v>
-      </c>
-      <c r="D27" t="n">
-        <v>-0.1629057954508097</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.8305797872298852</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.3655315642954129</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.9290167259985356</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1.275313646485168</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.8916400637841907</v>
+      <c r="C32" t="n">
+        <v>0.8326469129607912</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-0.03945935810783342</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.829011691999447</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.474646452617587</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.068329015939158</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.19589475548658</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9902766826703604</v>
       </c>
     </row>
   </sheetData>
